--- a/www/download/COUNTRY.KOR.rpA1.xlsx
+++ b/www/download/COUNTRY.KOR.rpA1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>Coreia do Sul</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>769.230769191585</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>806.451604195844</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>934.579434669612</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>1388.88887012112</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>1190.47621025982</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>1136.36362231776</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>1298.70133322324</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>1250.00002742103</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>1190.47619916019</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1149.42530127868</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>1020.40814942861</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>952.380984338174</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>925.925956818682</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>1081.23300950843</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>1270.08966179751</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20.398</t>
+          <t>0.102888041945791</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20.837</t>
+          <t>0.150576528227607</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21.201</t>
+          <t>0.280343773274637</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19.918</t>
+          <t>0.448631599562988</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20.277</t>
+          <t>0.52828749567508</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>21.136</t>
+          <t>0.469010782847079</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>21.557</t>
+          <t>0.445589996885508</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>22.152</t>
+          <t>0.487907933248531</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>22.117</t>
+          <t>0.40682154316995</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>22.534</t>
+          <t>0.42336186773556</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>0.388334905252529</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>23.133</t>
+          <t>0.349126131031146</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>23.418</t>
+          <t>0.383419623015692</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>23.561</t>
+          <t>0.509580426012997</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>0.587180397839265</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12.899</t>
+          <t>1.00353302658387</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>1.0461449614557</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13.405</t>
+          <t>1.25545487112779</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12.296</t>
+          <t>1.53780585085848</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>12.663</t>
+          <t>1.62250558413571</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13.361</t>
+          <t>1.49419272844156</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13.659</t>
+          <t>1.57275083740123</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14.182</t>
+          <t>1.49710708588125</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14.403</t>
+          <t>1.33487272770161</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>14.894</t>
+          <t>1.33445459658902</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>15.186</t>
+          <t>1.3497042369984</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>15.551</t>
+          <t>1.27838496065283</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>15.97</t>
+          <t>1.31850171378235</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>16.067</t>
+          <t>1.53632210875849</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>16.019</t>
+          <t>1.68786909587815</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>51162.193</t>
+          <t>1.24186718239878</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>50854.307</t>
+          <t>1.33586114366829</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>51302.684</t>
+          <t>1.58632554289444</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48438.841</t>
+          <t>1.92420891460249</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>50338.267</t>
+          <t>1.91302313429585</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>51635.805</t>
+          <t>1.83361590650058</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>52111.252</t>
+          <t>2.041875681485</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>53200.369</t>
+          <t>2.00231924770335</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>53124.252</t>
+          <t>1.82227555875435</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>55887.331</t>
+          <t>1.84460629583478</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>54220.887</t>
+          <t>1.7436247403155</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>54641.266</t>
+          <t>1.66618868484313</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>53454.996</t>
+          <t>1.72726514378811</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>53781.163</t>
+          <t>1.9812254482075</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>53619.22</t>
+          <t>2.17729878774531</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>32640.761</t>
+          <t>82855312076.1908</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>32366.566</t>
+          <t>83117095608.1248</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>32542.482</t>
+          <t>81621534455.8094</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>29972.52</t>
+          <t>69542036597.6117</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>31616.61</t>
+          <t>75388532833.8487</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>32772.416</t>
+          <t>81245800072.2372</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>33139.63</t>
+          <t>78979347688.6637</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>34146.109</t>
+          <t>80462900677.2937</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>34675.124</t>
+          <t>82958719990.6911</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>37056.547</t>
+          <t>89646513535.2384</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>36350.538</t>
+          <t>89730615679.3667</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>36940.81</t>
+          <t>94077891245.7855</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>36652.904</t>
+          <t>94257103885.9692</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>36876.55</t>
+          <t>97040004432.9099</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>36765.509</t>
+          <t>88964013500.651</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>33.17</t>
+          <t>19870238735.8992</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>19356813043.273</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>17753367035.9284</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>14788414014.8811</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>15128464887.3635</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>39.99</t>
+          <t>16359770609.8267</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>16615458376.4148</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>45.77</t>
+          <t>17410752956.2594</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>18876922861.6771</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>20134113553.5136</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>20262715745.5019</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>21239472684.0539</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>20641072435.0305</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>19013474581.2938</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>17967594574.6468</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>2834949.49940005</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>2645052.93407152</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>43.56</t>
+          <t>2778124.56956262</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>3273322.84204958</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>2893286.31484983</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>2763548.61738719</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>41.81</t>
+          <t>2944264.95137069</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>2706805.78907168</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>2503445.04427348</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>2298071.02932103</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>1911373.48529223</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>1747270.01857297</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>1556553.88842868</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>1560008.66602058</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>1651004.55545206</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>222783.020992882</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>218199.748124386</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>213414.595772775</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>195130.834275412</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>208689.176797465</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>218888.768075045</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>209656.584013131</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>10.99</t>
+          <t>214818.996267675</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>232549.667979935</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>265752.20165282</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>272918.920873113</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>285062.483815021</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>314565.535077353</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>350405.149077876</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>325879.897796837</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>644980.071881021</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>651859.518766038</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>636020.870106034</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>538957.752690119</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>608486.888497189</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>32.71</t>
+          <t>669344.649559848</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>633564.85441936</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>37.27</t>
+          <t>659842.106012385</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>732865.99845117</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>872798.716064598</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>935619.401444167</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>1028146.2919226</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>1165240.8079673</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>1328219.49377959</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>1135874.11336898</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>0.642695946653796</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.77</t>
+          <t>0.672102028726677</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>0.833031534836519</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>46.59</t>
+          <t>1.02675686604677</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>45.99</t>
+          <t>1.08987563790913</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>46.76</t>
+          <t>1.00323201325289</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>0.994505936813173</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>0.96120805710772</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>0.836905548736755</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>46.21</t>
+          <t>0.840485649555912</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>0.793961796019516</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>0.739252699311967</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>0.775726725810393</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>0.93949557787083</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>1.04621207069465</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>145883.213984109</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>158021.42916051</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>150136.590747949</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>108933.929406134</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>133260.804699939</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>152461.199303685</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>16.15</t>
+          <t>136306.255719661</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>150949.507231172</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>166236.839270636</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>179758.671079501</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>208079.568811872</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>234989.61719292</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>255150.264156843</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>247664.328440945</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>222593.277422626</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>769.230769191585</t>
+          <t>1540.44799875178</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>806.451604195844</t>
+          <t>1466.42523055099</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>934.579434669612</t>
+          <t>1324.38396388872</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1388.88887012112</t>
+          <t>1202.7012048537</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1190.47621025982</t>
+          <t>1194.69832483325</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1136.36362231776</t>
+          <t>1224.44207842427</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1298.70133322324</t>
+          <t>1216.44764451386</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1250.00002742103</t>
+          <t>1227.66555889574</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1190.47619916019</t>
+          <t>1310.62437420517</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1149.42530127868</t>
+          <t>1351.82714875209</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1020.40814942861</t>
+          <t>1334.30236701579</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>952.380984338174</t>
+          <t>1365.79465526679</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>925.925956818682</t>
+          <t>1292.49044677711</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1081.23300950843</t>
+          <t>1183.35398924513</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1270.08966179751</t>
+          <t>1121.63830038281</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>10935578893.3598</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>11907454173.1691</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>12044102943.6059</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>9333458584.39296</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>11592900140.5946</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>13156864586.0953</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>13567594841.8268</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>16309118573.4028</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>18557529856.8955</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>21289668935.2603</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>21548238387.4102</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>22826364896.0207</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>22966152210.32</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>18034879706.2495</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>16372947622.9747</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>10602879760.5557</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>11844513034.1074</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>12101096191.8498</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>9060014484.82636</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>11653896446.8957</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>13814436825.9972</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>14220719955.1323</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>17020161960.7425</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>19222584484.8626</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>21846497148.3961</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>22222817351.6523</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>23736382879.1952</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>23844473548.0852</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>19342271400.1063</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>17209214212.8642</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.761</t>
+          <t>332699132.804129</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>62941139.0617698</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.816</t>
+          <t>-56993248.2438738</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.339</t>
+          <t>273444099.566593</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.562</t>
+          <t>-60996306.3010065</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.701</t>
+          <t>-657572239.901917</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>-653125113.305418</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.799</t>
+          <t>-711043387.339647</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.104</t>
+          <t>-665054627.967043</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.357</t>
+          <t>-556828213.135782</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2.795</t>
+          <t>-674578964.242083</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3.142</t>
+          <t>-910017983.174563</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3.441</t>
+          <t>-878321337.765254</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3.361</t>
+          <t>-1307391693.8568</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3.066</t>
+          <t>-836266589.889515</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.109</t>
+          <t>2530.48768358049</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>2452.01260298029</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.132</t>
+          <t>2427.63757003982</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>2437.58292473996</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.995</t>
+          <t>2496.77092371987</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.154</t>
+          <t>2452.84156987341</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.075</t>
+          <t>2426.2120488053</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>2407.70758553998</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.373</t>
+          <t>2407.49318528712</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>2488.01846795831</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.914</t>
+          <t>2393.68747076475</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2.185</t>
+          <t>2375.46204087862</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.451</t>
+          <t>2295.10982919673</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.409</t>
+          <t>2295.10982919673</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.087</t>
+          <t>2295.10982919673</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>2508.19654903997</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>2440.5771832087</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>2419.82376783477</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>2431.91289060475</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>2482.530329715</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>2443.02633205807</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>2417.37033627695</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>2401.60567988671</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>2401.96463982723</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>2480.13361301885</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>2374.98409023748</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>2362.04840706289</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.945</t>
+          <t>2282.64563697712</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>2282.64563697712</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>2282.64563697712</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>148197.732393644</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>154555.396206786</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>168054.217503683</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>154804.50024608</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>52.83</t>
+          <t>166448.652207662</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>199000.056707812</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>44.56</t>
+          <t>174125.463571877</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>186166.474305133</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>223611.742831462</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>289120.505801717</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>38.83</t>
+          <t>327909.56113519</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>34.91</t>
+          <t>373577.44620443</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>38.34</t>
+          <t>436153.453196744</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>50.96</t>
+          <t>494948.776622255</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>407710.185299997</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>100.35</t>
+          <t>13617618750.66</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>104.61</t>
+          <t>13311373185.2095</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>125.55</t>
+          <t>14885016413.35</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>153.78</t>
+          <t>15595772828.5244</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>162.25</t>
+          <t>14784443585.8935</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>149.42</t>
+          <t>16095477402.7645</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>157.28</t>
+          <t>15360895541.7687</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>149.71</t>
+          <t>14743580335.5943</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>133.49</t>
+          <t>16234373581.8641</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>133.45</t>
+          <t>18955693496.2031</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>134.97</t>
+          <t>18104973480.8168</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>127.84</t>
+          <t>18972890456.8882</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>131.85</t>
+          <t>19879113074.1727</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>153.63</t>
+          <t>22577634070.4121</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>168.79</t>
+          <t>19959420030.3426</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>124.19</t>
+          <t>140581.430961096</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>133.59</t>
+          <t>157516.01026986</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>158.63</t>
+          <t>157672.57675118</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>192.42</t>
+          <t>106221.758194344</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>191.3</t>
+          <t>130177.744039377</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>183.36</t>
+          <t>173153.47173526</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>204.19</t>
+          <t>153240.259906808</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>200.23</t>
+          <t>164700.969649037</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>182.23</t>
+          <t>193962.743807858</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>184.46</t>
+          <t>240516.625421563</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>174.36</t>
+          <t>281709.808589289</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>166.62</t>
+          <t>331011.002020373</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>172.73</t>
+          <t>385382.978704207</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>198.12</t>
+          <t>473784.922435432</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>217.73</t>
+          <t>352512.873467787</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>51162.193</t>
+          <t>23377105828.0569</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50854.307</t>
+          <t>25657669392.1186</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>51302.684</t>
+          <t>25508384258.7206</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>48438.841</t>
+          <t>17930666951.7239</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>50338.267</t>
+          <t>21034496084.4457</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>51635.805</t>
+          <t>25415326096.2095</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>52111.252</t>
+          <t>25668229663.0358</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>53200.369</t>
+          <t>27739173400.5859</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>53124.252</t>
+          <t>30474064507.3311</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>55887.331</t>
+          <t>33754552966.0199</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>54220.887</t>
+          <t>33934323158.5599</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>54641.266</t>
+          <t>36993364272.1338</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>53454.996</t>
+          <t>37790971594.1664</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>53781.163</t>
+          <t>38747678073.4476</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>53619.22</t>
+          <t>30984656716.1824</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>32640.761</t>
+          <t>7616.30143254875</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>32366.566</t>
+          <t>-2960.61406307348</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>32542.482</t>
+          <t>10381.6407525029</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>29972.52</t>
+          <t>48582.7420517361</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>31616.61</t>
+          <t>36270.9081682852</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>32772.416</t>
+          <t>25846.5849725521</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>33139.63</t>
+          <t>20885.2036650692</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>34146.109</t>
+          <t>21465.5046560963</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>34675.124</t>
+          <t>29648.9990236033</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>37056.547</t>
+          <t>48603.8803801539</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>36350.538</t>
+          <t>46199.752545901</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>36940.81</t>
+          <t>42566.4441840567</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>36652.904</t>
+          <t>50770.4744925373</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>36876.55</t>
+          <t>21163.8541868228</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>36765.509</t>
+          <t>55197.31183221</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>82855.312</t>
+          <t>-9759487077.39692</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>83117.096</t>
+          <t>-12346296206.9091</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>81621.534</t>
+          <t>-10623367845.3705</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69542.037</t>
+          <t>-2334894123.19952</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>75388.533</t>
+          <t>-6250052498.55217</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>81245.8</t>
+          <t>-9319848693.44492</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>78979.348</t>
+          <t>-10307334121.2671</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>80462.901</t>
+          <t>-12995593064.9916</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>82958.72</t>
+          <t>-14239690925.467</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>89646.514</t>
+          <t>-14798859469.8168</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>89730.616</t>
+          <t>-15829349677.743</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>94077.891</t>
+          <t>-18020473815.2456</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>94257.104</t>
+          <t>-17911858519.9937</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>97040.004</t>
+          <t>-16170044003.0355</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>88964.014</t>
+          <t>-11025236685.8398</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>274121.89465</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.652</t>
+          <t>287499.72846</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>268282.01642</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>180435.22768</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>227489.32958</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>259521.41133</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>240708.48946</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>270796.19484</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>307219.55963</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.873</t>
+          <t>357054.9163</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.936</t>
+          <t>416922.20117</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.028</t>
+          <t>466492.72549</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>515376.82677</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>459994.19235</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.136</t>
+          <t>409732.13588</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>28619.112</t>
+          <t>-0.0311037571734734</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>27822.144</t>
+          <t>-0.0389042557898944</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>27387.823</t>
+          <t>-0.0322019601810935</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25177.847</t>
+          <t>-0.0287825108329188</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>25855.563</t>
+          <t>-0.0205755306115161</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>26568.963</t>
+          <t>-0.0190265316174358</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>26135.509</t>
+          <t>-0.0188382346331709</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>26195.6</t>
+          <t>-0.0125069685025224</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>26324.079</t>
+          <t>-0.0126584369473392</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>27295.822</t>
+          <t>-0.0040949701678003</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>26174.3</t>
+          <t>-0.00512130265178204</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>26083.912</t>
+          <t>-0.00412105377931646</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>25445.415</t>
+          <t>0.00138864159816814</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>25600.676</t>
+          <t>-0.0050566809743088</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>25523.589</t>
+          <t>-0.00602637790458473</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>249110.987205519</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>272393.548705949</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>249618.697610976</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>161334.261309919</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>200645.101910896</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>229288.854944361</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>219964.217061377</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>250739.517668645</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>287975.197009048</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>322535.656092378</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>387647.803112496</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>440293.28298971</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>483677.734658298</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>439426.781156843</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>390590.697894541</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>19870.239</t>
+          <t>390388.35789602</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>19356.813</t>
+          <t>429108.845699053</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>17753.367</t>
+          <t>393881.896820065</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>14788.414</t>
+          <t>257613.676550789</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>15128.465</t>
+          <t>312348.682631458</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>16359.771</t>
+          <t>353831.571985482</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>16615.458</t>
+          <t>339803.996715696</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>17410.753</t>
+          <t>382243.187022735</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>18876.923</t>
+          <t>433445.671955757</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>20134.114</t>
+          <t>475287.804818375</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>20262.716</t>
+          <t>566607.454749689</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>21239.473</t>
+          <t>633380.066717064</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>20641.072</t>
+          <t>684836.2921322</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>19013.475</t>
+          <t>619922.388725574</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>17967.595</t>
+          <t>550345.838391702</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>64.27</t>
+          <t>1760829.1189605</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>67.21</t>
+          <t>1877338.60876306</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>1815958.90185428</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>102.68</t>
+          <t>1339132.81334857</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>108.99</t>
+          <t>1562163.15089374</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>100.32</t>
+          <t>1701353.49363953</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>99.45</t>
+          <t>1594994.15101507</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.12</t>
+          <t>1798851.73688326</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>83.69</t>
+          <t>2103913.66621226</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>84.05</t>
+          <t>2357180.08736089</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>2795229.38105993</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>73.93</t>
+          <t>3142233.58718998</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>77.57</t>
+          <t>3440728.34002697</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>93.95</t>
+          <t>3360863.6263319</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>3066435.03210023</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2.835</t>
+          <t>390388.35789602</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.645</t>
+          <t>428589.960716182</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.778</t>
+          <t>441970.169407685</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3.273</t>
+          <t>408004.34827534</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.893</t>
+          <t>427374.866036795</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.764</t>
+          <t>459218.408752575</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.944</t>
+          <t>485951.913102854</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.707</t>
+          <t>510733.843279555</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.503</t>
+          <t>533263.829689562</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.298</t>
+          <t>544828.800386899</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.911</t>
+          <t>577464.20665302</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.747</t>
+          <t>605129.469906568</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>632759.282473243</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>654996.466782229</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.651</t>
+          <t>660805.520872823</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>249110.987205519</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>271693.846620992</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>277965.695940862</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>251566.758518966</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>274181.471253126</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>297858.188855432</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>314883.476316144</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>336240.636147866</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>357353.197563222</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>372975.201836446</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>397365.382260671</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>424694.737027864</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>448762.49721263</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>464523.411320782</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>468407.377087872</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>91114.8126439805</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>84984.9677209469</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>91659.1544999351</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>70390.3246992115</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>101118.468968542</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>120090.343264518</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>106259.381664304</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>128451.325217265</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>139604.580784243</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>170106.088941625</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>193764.353170311</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>222040.303592935</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>259928.2026578</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>230669.513284426</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>204113.781099333</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>32640760630.5048</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>32366566359.3398</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>32542481626.3838</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>29972519642.6025</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>31616610207.0647</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>32772416215.0786</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>33139630374.6316</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>34146108978.1279</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>34675124347.6904</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>37056547061.771</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>36350537931.0334</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>36940810197.7035</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>36652903972.2718</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>36876549870.3788</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>36765508899.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>51162193207.3174</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>50854306766.5198</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>51302683701.8651</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>48438840955.0654</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>50338267495.631</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>51635804554.3794</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>52111252339.1222</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>53200369020.8505</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>53124251939.0588</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>55887330835.7667</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>54220886780.1216</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>54641265800.5858</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>53454995526.7301</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>53781163147.4982</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>53619219783.3406</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>28619111712.7211</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>27822143889.0005</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>27387822634.399</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>25177846595.1586</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>25855562633.2732</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>26568962791.8559</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>26135509456.5117</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>26195599527.1957</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>26324079477.8952</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>27295821939.2313</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>26174299894.4793</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>26083911950.3647</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>25445415330.4625</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>25600676227.8962</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>25523588649.4501</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>20398000</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>20837000</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>21201000</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>19918000</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>20277000</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>21136000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>21557000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>22152000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>22117000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>22534000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>22830000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>23133000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>23418000</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>23560890.1689708</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>23489944.7004608</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>12899000</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>13200000</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>13405000</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>12296000</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>12663000</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>13361000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>13659000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>14182000</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>14403000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>14894000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>15186000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>15551000</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>15970000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>16067444.5297832</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>16019062.9800307</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>51162193207.3174</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>50854306766.5198</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>51302683701.8651</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>48438840955.0654</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>50338267495.631</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>51635804554.3794</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>52111252339.1222</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>53200369020.8505</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>53124251939.0588</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>55887330835.7667</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>54220886780.1216</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>54641265800.5858</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>53454995526.7301</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>53781163147.4982</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>53619219783.3406</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>32640760630.5048</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>32366566359.3398</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>32542481626.3838</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>29972519642.6025</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>31616610207.0647</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>32772416215.0786</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>33139630374.6316</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>34146108978.1279</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>34675124347.6904</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>37056547061.771</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>36350537931.0334</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>36940810197.7035</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>36652903972.2718</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>36876549870.3788</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>36765508899.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.331716691795572</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.354037887688592</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.360021341046824</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.385882898215127</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.39689266710716</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.399947745631216</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.427682288313345</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.457678077948967</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.463015386857404</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.469383418714181</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.490009375601123</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.490009375601123</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.490009375601123</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.490009375601123</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.490009375601123</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.436166942521148</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.430448852721004</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.435615610218396</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.42882899269932</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.419954649183771</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.427606828039</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.418059720586339</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.403877621841788</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.403828393058087</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.410036099509903</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.395258537696225</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.395258537696225</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.395258537696225</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.395258537696225</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.395258537696225</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.203544937111852</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.186941831018976</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.175791620163351</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.156716680514124</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.15458125513764</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.143873997758355</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.125686562528887</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.109872871637817</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.10458479151308</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0920090532044868</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0861606581312238</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0861606581312238</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0861606581312238</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0861606581312238</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0861606581312238</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.264457196852025</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.279162503358605</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.289349291432411</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.313902096132527</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.325542157096532</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.32708265847282</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.342450577055497</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.372650802730414</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.379068724074233</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.385820132625152</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.398516741084111</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.398516741084111</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.398516741084111</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.398516741084111</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.398516741084111</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.468885762181886</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.46768117868951</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.470119431690414</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.465859789604328</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.459922710933326</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.467590107354008</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.467462732560993</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.456048864718562</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.455280579791477</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.462053049660315</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.459232263808909</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.459232263808909</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.459232263808909</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.459232263808909</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.459232263808909</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.23808561239466</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.224584889380456</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.211959848305746</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.191666685691717</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.185963703398713</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.176755805601743</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.161515261812081</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.142728903979596</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.137079267562861</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.123555389143104</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.113679566535551</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.113679566535551</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.113679566535551</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.113679566535551</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.113679566535551</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1108509.34671</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1192915.35281</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1131548.8462</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>789859.03294</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>995264.19459</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1154386.08155</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1074724.66787</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1220729.34865</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1373053.82031</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1590214.92382</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1913875.12857</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2184540.4385</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2450518.8305</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2409391.66177</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2086877.38964</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>481503.17054</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>514093.81342</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>485541.05132</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>328004.00125</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>413467.1516</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>473921.91525</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>446063.37838</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>510694.51224</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>573050.25274</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>645393.89376</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>760371.80792</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>855420.37031</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>944764.49479</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>850591.90201</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>754935.69005</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1354483967.86827</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1457969032.78694</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1552067726.24768</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1607502307.4535</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1670427170.49331</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1744651239.55253</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1816305945.149</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1895039613.93994</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1977196331.69843</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2058958231.97673</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2140992828.15616</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2225192944.02245</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2313261489.50933</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2392646349.28768</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2465814200.56571</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
